--- a/_passla/inputs/LAUNCH KS4 - 2026-27.xlsx
+++ b/_passla/inputs/LAUNCH KS4 - 2026-27.xlsx
@@ -1196,7 +1196,7 @@
     <t>Wellbeing for all and reducing stigma (PSHE / PE).</t>
   </si>
   <si>
-    <t>SUMMER TERM 2  ·  June, end of academic year 2027</t>
+    <t>SUMMER TERM 2  ·  21 July, end of academic year 2027</t>
   </si>
   <si>
     <t>Throughout June</t>
